--- a/green-holloway_territory_chart.xlsx
+++ b/green-holloway_territory_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\Data_Labs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4288A90-6546-4F8C-9E0C-3B909A9A8F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865B2BA2-FDFE-4248-9296-19A258AA04BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,14 +823,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr/>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -948,14 +940,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1054,14 +1038,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1178,14 +1154,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr/>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1351,14 +1319,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1457,14 +1417,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1544,1280 +1496,6 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="bg1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-        <a:headEnd type="none" w="sm" len="sm"/>
-        <a:tailEnd type="none" w="sm" len="sm"/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="bg1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-          <a:gs pos="75000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="51000">
-            <a:schemeClr val="phClr">
-              <a:alpha val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-              <a:alpha val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-        <a:headEnd type="none" w="sm" len="sm"/>
-        <a:tailEnd type="none" w="sm" len="sm"/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/green-holloway_territory_chart.xlsx
+++ b/green-holloway_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\Data_Labs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865B2BA2-FDFE-4248-9296-19A258AA04BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ADE72E-5AD5-4FAD-A4D9-489DCD20C8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="green-holloway_territory_chart" sheetId="1" r:id="rId1"/>
@@ -2220,7 +2220,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="83.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>

--- a/green-holloway_territory_chart.xlsx
+++ b/green-holloway_territory_chart.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\Data_Labs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ADE72E-5AD5-4FAD-A4D9-489DCD20C8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFC6D9F-FA9C-4F58-9ECE-197539B11C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="green-holloway_territory_chart" sheetId="1" r:id="rId1"/>
     <sheet name="East PivotCharts" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="59">
   <si>
     <t>StoreId</t>
   </si>
@@ -110,9 +123,6 @@
     <t>Old Saybrook</t>
   </si>
   <si>
-    <t>East Region PivotChart Analysis</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -161,20 +171,58 @@
     <t>Recommendation</t>
   </si>
   <si>
-    <t>Focus next quarter on New York and the top stores (New York and Rochester). They bring in the strongest revenue, so extra inventory, promotions, and sales support there could create the biggest impact. Connecticut should still be reviewed for opportunities to lift lower-performing stores.</t>
-  </si>
-  <si>
-    <t>Curated from query results to make East region performance easier to compare.</t>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Product Category</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Technology &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Textbooks</t>
+  </si>
+  <si>
+    <t>Apparel and Merchandise</t>
+  </si>
+  <si>
+    <t>Art Supplies</t>
+  </si>
+  <si>
+    <t>Books (General)</t>
+  </si>
+  <si>
+    <t>Stationery and Supplies</t>
+  </si>
+  <si>
+    <t>Stamford</t>
+  </si>
+  <si>
+    <t>Lower-Performing Stores to Review</t>
+  </si>
+  <si>
+    <t>Top-Performing Stores to Review</t>
+  </si>
+  <si>
+    <t>East Region(Connecticut) Analysis</t>
+  </si>
+  <si>
+    <t>For Connecticut and lower-performing stores, the company could try better promotions, stronger product displays, and more focus on higher-value items.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,13 +328,17 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF4B5563"/>
-      <name val="Aptos Narrow"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,8 +533,19 @@
         <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -663,6 +726,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -708,10 +806,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -730,6 +827,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -907,8 +1014,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="355"/>
-        <c:overlap val="-70"/>
+        <c:gapWidth val="150"/>
         <c:axId val="48650112"/>
         <c:axId val="48672768"/>
       </c:barChart>
@@ -919,28 +1025,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Revenue</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1045,9 +1129,6 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
@@ -1074,6 +1155,12 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1503,11 +1590,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:colOff>12699</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6000750" cy="2600325"/>
+    <xdr:ext cx="6697133" cy="2600325"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -1534,11 +1621,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>10583</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>77259</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6096000" cy="3390900"/>
+    <xdr:ext cx="6699250" cy="3390900"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart">
@@ -1721,491 +1808,491 @@
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>850</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>624274.57999999996</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>4484</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>847</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>607996.30000000005</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>4392</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>846</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>334908.03999999998</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>2190</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>870</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>331187.34999999998</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>2277</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>865</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>324611.48</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>2237</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>841</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>315453.67</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>2241</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>842</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>314352.74</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>2197</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>843</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>314205.52</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>2233</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>867</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>311970.57</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>2141</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>845</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>311969.48</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>2149</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>840</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>310778.98</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>2309</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>848</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>309462.93</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>2280</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>849</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>305278.82</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>2302</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>844</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>303515.36</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>2180</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>872</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>295985.59999999998</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>2104</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>851</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>290171.90999999997</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>2149</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>868</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>287486.69</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>2133</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>869</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>286865.40999999997</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>2175</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>866</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>284023.25</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>2157</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>871</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>279399.26</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>2196</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>20</v>
       </c>
     </row>
@@ -2216,21 +2303,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="83.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
     <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2239,368 +2330,693 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="3" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6743897.9400000004</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4342368.33</v>
+      </c>
+      <c r="F4" s="5">
+        <v>31106</v>
+      </c>
+      <c r="G4" s="4">
+        <v>139.6</v>
+      </c>
+      <c r="H4" s="4">
+        <v>361864.03</v>
+      </c>
+      <c r="S4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="T4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="U4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5">
+        <v>48526</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2401529.61</v>
+      </c>
+      <c r="F5" s="5">
+        <v>17420</v>
+      </c>
+      <c r="G5" s="4">
+        <v>137.86000000000001</v>
+      </c>
+      <c r="H5" s="4">
+        <v>300191.2</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U5" s="15">
+        <v>277310.18</v>
+      </c>
+      <c r="V5" s="16">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="4">
+        <v>138.97</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U6" s="15">
+        <v>283455.62</v>
+      </c>
+      <c r="V6" s="16">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="15">
+        <v>286217.15000000002</v>
+      </c>
+      <c r="V7" s="16">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U8" s="15">
+        <v>286779.43</v>
+      </c>
+      <c r="V8" s="16">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S9" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V10" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S11" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="T11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U11" s="15">
+        <v>331116.76</v>
+      </c>
+      <c r="V11" s="16">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="5">
-        <v>6743897.9400000004</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="S12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="T12" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U12" s="15">
+        <v>322100.07</v>
+      </c>
+      <c r="V12" s="16">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3">
+        <v>850</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4">
+        <v>624274.57999999996</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4484</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5">
-        <v>4342368.33</v>
-      </c>
-      <c r="F5" s="6">
-        <v>31106</v>
-      </c>
-      <c r="G5" s="5">
-        <v>139.6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>361864.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="6">
-        <v>48526</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="U13" s="15">
+        <v>318111.55</v>
+      </c>
+      <c r="V13" s="16">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3">
+        <v>847</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4">
+        <v>607996.30000000005</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4392</v>
+      </c>
+      <c r="S14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="T14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4">
+      <c r="U14" s="15">
+        <v>308421.23</v>
+      </c>
+      <c r="V14" s="16">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3">
+        <v>846</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>334908.03999999998</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3">
+        <v>870</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="4">
+        <v>331187.34999999998</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>5</v>
+      </c>
+      <c r="B17" s="3">
+        <v>865</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="4">
+        <v>324611.48</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>6</v>
+      </c>
+      <c r="B18" s="3">
+        <v>841</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4">
+        <v>315453.67</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>7</v>
+      </c>
+      <c r="B19" s="3">
+        <v>842</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="4">
+        <v>314352.74</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>8</v>
       </c>
-      <c r="E6" s="5">
-        <v>2401529.61</v>
-      </c>
-      <c r="F6" s="6">
-        <v>17420</v>
-      </c>
-      <c r="G6" s="5">
-        <v>137.86000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <v>300191.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5">
-        <v>138.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B20" s="3">
+        <v>843</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="E20" s="4">
+        <v>314205.52</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3">
+        <v>867</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="4">
+        <v>311970.57</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>10</v>
+      </c>
+      <c r="B22" s="3">
+        <v>845</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="E22" s="4">
+        <v>311969.48</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4">
-        <v>850</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="5">
-        <v>624274.57999999996</v>
-      </c>
-      <c r="F14" s="6">
-        <v>4484</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>2</v>
-      </c>
-      <c r="B15" s="4">
-        <v>847</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5">
-        <v>607996.30000000005</v>
-      </c>
-      <c r="F15" s="6">
-        <v>4392</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4">
-        <v>846</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="5">
-        <v>334908.03999999998</v>
-      </c>
-      <c r="F16" s="6">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4">
-        <v>870</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="5">
-        <v>331187.34999999998</v>
-      </c>
-      <c r="F17" s="6">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>5</v>
-      </c>
-      <c r="B18" s="4">
-        <v>865</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="5">
-        <v>324611.48</v>
-      </c>
-      <c r="F18" s="6">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>6</v>
-      </c>
-      <c r="B19" s="4">
-        <v>841</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="5">
-        <v>315453.67</v>
-      </c>
-      <c r="F19" s="6">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>7</v>
-      </c>
-      <c r="B20" s="4">
-        <v>842</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="5">
-        <v>314352.74</v>
-      </c>
-      <c r="F20" s="6">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>8</v>
-      </c>
-      <c r="B21" s="4">
-        <v>843</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="5">
-        <v>314205.52</v>
-      </c>
-      <c r="F21" s="6">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>9</v>
-      </c>
-      <c r="B22" s="4">
-        <v>867</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="5">
-        <v>311970.57</v>
-      </c>
-      <c r="F22" s="6">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>10</v>
-      </c>
-      <c r="B23" s="4">
-        <v>845</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="5">
-        <v>311969.48</v>
-      </c>
-      <c r="F23" s="6">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="E27" s="17"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="14">
+        <v>4779056.6900000004</v>
+      </c>
+      <c r="D28" s="13">
+        <v>10117</v>
+      </c>
+      <c r="E28" s="15"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="14">
+        <v>1175355.25</v>
+      </c>
+      <c r="D29" s="13">
+        <v>6785</v>
+      </c>
+      <c r="E29" s="15"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="14">
+        <v>305367.03000000003</v>
+      </c>
+      <c r="D30" s="13">
+        <v>9525</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="14">
+        <v>249883.83</v>
+      </c>
+      <c r="D31" s="13">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="14">
+        <v>110512.08</v>
+      </c>
+      <c r="D32" s="13">
+        <v>3830</v>
+      </c>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="14">
+        <v>102864.65</v>
+      </c>
+      <c r="D33" s="13">
+        <v>10268</v>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="16"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F32:I32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C28:C33">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF059669"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF059669"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6B86B220-14BB-4B6A-B9CC-2AB62747B02B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U11:U14">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF2563EB"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF2563EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2C263492-29CB-42A6-BA7B-C605391E80E9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6B86B220-14BB-4B6A-B9CC-2AB62747B02B}">
+            <x14:dataBar>
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor auto="1"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C28:C33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2C263492-29CB-42A6-BA7B-C605391E80E9}">
+            <x14:dataBar>
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor auto="1"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>U11:U14</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>